--- a/data/output/2025/evaluasi_75.xlsx
+++ b/data/output/2025/evaluasi_75.xlsx
@@ -813,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1069,6 +1069,174 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>4.035840039334142</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>42.97110767629606</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.56477023214778</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-5.953721544122763</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>0.3994942747542055</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7501</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Boalemo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.2779271319280545</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1395,6 +1563,258 @@
       <c r="F11" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-8.935892340652222</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2.94873331097357</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>38.35883487616027</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>14.38193788048551</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1.748461714514261</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1.704475031536738</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-2.979573334671707</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-2.100348417661631</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7502</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.6684476881866325</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkrt_2025_prov vs implisit_y-on-y_pkrt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1409,7 +1829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1833,6 +2253,174 @@
       <c r="F15" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>2.140672783200003</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-9.609858476836406</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-3.794121921950435</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1865949491313975</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>-0.09319619067627148</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>7503</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Kabupaten Pohuwato</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>0.1641752469383195</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1847,7 +2435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2103,6 +2691,230 @@
       <c r="F9" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.20333939988557</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.223382066396213</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.98779067325539</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>34.5417673743903</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.387007044547005</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-2.082019988759707</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>0.263544468413458</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7505</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Gorontalo Utara</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>9.92926165449018</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q4-25_prov vs implisit_y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2929,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2317,6 +3129,202 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7571</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-7.763796725928697</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7571</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>27.71847706172981</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7571</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>7.470018470439618</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7571</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-2.31855553676171</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7571</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>0.3629136898885956</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7571</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.003728063126353</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7571</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Gorontalo</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.332498145980968</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_2025_prov vs implisit_y-on-y_pklnprt_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2331,7 +3339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2377,20 +3385,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-4.329920863973616</v>
+        <v>-8.136867134167778</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2405,18 +3413,298 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-0.1282824274506966</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.491406815887494</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>66.24516265524841</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.62875317242185</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.70067406028231</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.367362168480963</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>19.32917263610968</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-7.911798845271369</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-4.020324713270288</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-4.329920863973616</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7504</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Bone Bolango</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>-2.399297395826653</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_q4-25</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
